--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/color_theme_pref.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/color_theme_pref.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C2" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>9.5</v>
+        <v>8.48</v>
       </c>
     </row>
   </sheetData>
